--- a/predicciones_reporte_completo.xlsx
+++ b/predicciones_reporte_completo.xlsx
@@ -58,8 +58,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
-        <bgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -70,14 +70,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-        <bgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FCE4D6"/>
+        <bgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -565,7 +565,7 @@
         <v>7</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>6.110000133514404</v>
+        <v>7.550000190734863</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
@@ -574,7 +574,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -593,7 +593,7 @@
         <v>7</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>4.800000190734863</v>
+        <v>5.389999866485596</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -621,14 +621,14 @@
         <v>7</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>6.090000152587891</v>
+        <v>6.159999847412109</v>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>A-</t>
         </is>
@@ -649,14 +649,14 @@
         <v>7</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>5.840000152587891</v>
+        <v>6.389999866485596</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>A-</t>
         </is>
@@ -677,14 +677,14 @@
         <v>7</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>6.010000228881836</v>
+        <v>6.170000076293945</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>A-</t>
         </is>
@@ -705,16 +705,16 @@
         <v>7</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>6.380000114440918</v>
+        <v>6.639999866485596</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>A-</t>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -733,16 +733,16 @@
         <v>7</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>6.420000076293945</v>
+        <v>6.710000038146973</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>A-</t>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -761,14 +761,14 @@
         <v>7</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>5.659999847412109</v>
+        <v>6.21999979019165</v>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>A-</t>
         </is>
@@ -789,14 +789,14 @@
         <v>7</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>5.639999866485596</v>
+        <v>6.159999847412109</v>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>A-</t>
         </is>
@@ -817,16 +817,16 @@
         <v>9</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+        <v>8.039999961853027</v>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -845,16 +845,16 @@
         <v>9</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>8.649999618530273</v>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+        <v>7.21999979019165</v>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -873,16 +873,16 @@
         <v>9</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>8.640000343322754</v>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+        <v>7.090000152587891</v>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -901,16 +901,16 @@
         <v>9</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>8.579999923706055</v>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+        <v>7.320000171661377</v>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -929,14 +929,14 @@
         <v>9</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>8.489999771118164</v>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
+        <v>7.639999866485596</v>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -957,14 +957,14 @@
         <v>9</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>8.489999771118164</v>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
+        <v>7.940000057220459</v>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -985,16 +985,16 @@
         <v>9</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>8.569999694824219</v>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+        <v>7.920000076293945</v>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -1013,16 +1013,16 @@
         <v>9</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>8.770000457763672</v>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+        <v>8.220000267028809</v>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -1041,16 +1041,16 @@
         <v>9</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+        <v>8.149999618530273</v>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -1069,16 +1069,16 @@
         <v>9</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>8.979999542236328</v>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+        <v>8.390000343322754</v>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -1097,16 +1097,16 @@
         <v>9</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>8.960000038146973</v>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+        <v>8.029999732971191</v>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -1125,16 +1125,16 @@
         <v>9</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>8.949999809265137</v>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+        <v>7.980000019073486</v>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -1153,14 +1153,14 @@
         <v>9</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
+        <v>8.600000381469727</v>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -1181,16 +1181,16 @@
         <v>9</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>9.069999694824219</v>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+        <v>8.399999618530273</v>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -1209,14 +1209,14 @@
         <v>9</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>9.069999694824219</v>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F25" s="7" t="inlineStr">
+        <v>8.510000228881836</v>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -1237,14 +1237,14 @@
         <v>9</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>8.989999771118164</v>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="inlineStr">
+        <v>8.590000152587891</v>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -1265,16 +1265,16 @@
         <v>9</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+        <v>8.420000076293945</v>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -1293,14 +1293,14 @@
         <v>9</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>9.130000114440918</v>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="inlineStr">
+        <v>8.75</v>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -1321,14 +1321,14 @@
         <v>9</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>9.109999656677246</v>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="inlineStr">
+        <v>8.779999732971191</v>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -1349,14 +1349,14 @@
         <v>9</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>9.020000457763672</v>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="inlineStr">
+        <v>8.800000190734863</v>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -1377,14 +1377,14 @@
         <v>9</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>9.130000114440918</v>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F31" s="7" t="inlineStr">
+        <v>8.859999656677246</v>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -1405,14 +1405,14 @@
         <v>9</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>9.119999885559082</v>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F32" s="7" t="inlineStr">
+        <v>8.920000076293945</v>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -1433,14 +1433,14 @@
         <v>9</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>9.199999809265137</v>
-      </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F33" s="7" t="inlineStr">
+        <v>8.760000228881836</v>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -1461,14 +1461,14 @@
         <v>9</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>7.710000038146973</v>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F34" s="8" t="inlineStr">
+        <v>8.390000343322754</v>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -1489,16 +1489,16 @@
         <v>9</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>8.590000152587891</v>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+        <v>7.869999885559082</v>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -1517,16 +1517,16 @@
         <v>9</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>8.069999694824219</v>
-      </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F36" s="8" t="inlineStr">
-        <is>
-          <t>A+</t>
+        <v>6.929999828338623</v>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -1545,16 +1545,16 @@
         <v>9</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>7.820000171661377</v>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F37" s="8" t="inlineStr">
-        <is>
-          <t>A+</t>
+        <v>7.199999809265137</v>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -1573,16 +1573,16 @@
         <v>9</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>7.900000095367432</v>
-      </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F38" s="8" t="inlineStr">
-        <is>
-          <t>A+</t>
+        <v>6.860000133514404</v>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -1601,16 +1601,16 @@
         <v>9</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>7.909999847412109</v>
-      </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F39" s="8" t="inlineStr">
-        <is>
-          <t>A+</t>
+        <v>7.400000095367432</v>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -1629,14 +1629,14 @@
         <v>9</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F40" s="8" t="inlineStr">
+        <v>7.869999885559082</v>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -1657,14 +1657,14 @@
         <v>9</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>8.260000228881836</v>
-      </c>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F41" s="8" t="inlineStr">
+        <v>8.159999847412109</v>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -1685,14 +1685,14 @@
         <v>10</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>9.210000038146973</v>
+        <v>8.850000381469727</v>
       </c>
       <c r="E42" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F42" s="7" t="inlineStr">
+      <c r="F42" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -1713,14 +1713,14 @@
         <v>10</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>9.300000190734863</v>
+        <v>8.550000190734863</v>
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F43" s="7" t="inlineStr">
+      <c r="F43" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -1741,14 +1741,14 @@
         <v>10</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>9.430000305175781</v>
+        <v>8.619999885559082</v>
       </c>
       <c r="E44" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F44" s="7" t="inlineStr">
+      <c r="F44" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -1769,14 +1769,14 @@
         <v>10</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>9.359999656677246</v>
+        <v>8.859999656677246</v>
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F45" s="7" t="inlineStr">
+      <c r="F45" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -1797,14 +1797,14 @@
         <v>10</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>9.430000305175781</v>
+        <v>8.890000343322754</v>
       </c>
       <c r="E46" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F46" s="7" t="inlineStr">
+      <c r="F46" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -1825,14 +1825,14 @@
         <v>10</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>9.369999885559082</v>
+        <v>8.899999618530273</v>
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F47" s="7" t="inlineStr">
+      <c r="F47" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -1853,14 +1853,14 @@
         <v>10</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>9.409999847412109</v>
+        <v>8.880000114440918</v>
       </c>
       <c r="E48" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F48" s="7" t="inlineStr">
+      <c r="F48" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -1881,14 +1881,14 @@
         <v>10</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>9.359999656677246</v>
+        <v>8.859999656677246</v>
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F49" s="7" t="inlineStr">
+      <c r="F49" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -1909,14 +1909,14 @@
         <v>10</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>9.399999618530273</v>
+        <v>8.960000038146973</v>
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F50" s="7" t="inlineStr">
+      <c r="F50" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -1937,14 +1937,14 @@
         <v>10</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>9.359999656677246</v>
+        <v>8.840000152587891</v>
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F51" s="7" t="inlineStr">
+      <c r="F51" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -1965,14 +1965,14 @@
         <v>10</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>9.470000267028809</v>
+        <v>8.760000228881836</v>
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F52" s="7" t="inlineStr">
+      <c r="F52" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -1993,14 +1993,14 @@
         <v>10</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>9.300000190734863</v>
+        <v>9.079999923706055</v>
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F53" s="7" t="inlineStr">
+      <c r="F53" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -2021,14 +2021,14 @@
         <v>10</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>9.170000076293945</v>
+        <v>8.859999656677246</v>
       </c>
       <c r="E54" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F54" s="7" t="inlineStr">
+      <c r="F54" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -2049,14 +2049,14 @@
         <v>10</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>9.199999809265137</v>
+        <v>9.239999771118164</v>
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F55" s="7" t="inlineStr">
+      <c r="F55" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -2077,14 +2077,14 @@
         <v>10</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>9.130000114440918</v>
+        <v>9.020000457763672</v>
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F56" s="7" t="inlineStr">
+      <c r="F56" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -2105,14 +2105,14 @@
         <v>10</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>9.329999923706055</v>
+        <v>9.010000228881836</v>
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F57" s="7" t="inlineStr">
+      <c r="F57" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -2133,14 +2133,14 @@
         <v>10</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>9.439999580383301</v>
+        <v>9.060000419616699</v>
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F58" s="7" t="inlineStr">
+      <c r="F58" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -2161,14 +2161,14 @@
         <v>10</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>8.710000038146973</v>
+        <v>8.640000343322754</v>
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F59" s="7" t="inlineStr">
+      <c r="F59" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -2189,14 +2189,14 @@
         <v>10</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>9.25</v>
+        <v>8.779999732971191</v>
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F60" s="7" t="inlineStr">
+      <c r="F60" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -2217,14 +2217,14 @@
         <v>10</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>9.279999732971191</v>
+        <v>8.840000152587891</v>
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F61" s="7" t="inlineStr">
+      <c r="F61" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -2245,14 +2245,14 @@
         <v>10</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>9.310000419616699</v>
+        <v>8.970000267028809</v>
       </c>
       <c r="E62" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F62" s="7" t="inlineStr">
+      <c r="F62" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -2273,14 +2273,14 @@
         <v>10</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>9.310000419616699</v>
+        <v>8.970000267028809</v>
       </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F63" s="7" t="inlineStr">
+      <c r="F63" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -2301,16 +2301,16 @@
         <v>10</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>9.229999542236328</v>
+        <v>8.270000457763672</v>
       </c>
       <c r="E64" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F64" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -2329,16 +2329,16 @@
         <v>8</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>7.179999828338623</v>
-      </c>
-      <c r="E65" s="8" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
+        <v>6.320000171661377</v>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>A-</t>
         </is>
       </c>
     </row>
@@ -2357,9 +2357,9 @@
         <v>8</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>6.820000171661377</v>
-      </c>
-      <c r="E66" s="8" t="inlineStr">
+        <v>6.659999847412109</v>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -2385,9 +2385,9 @@
         <v>8</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>6.909999847412109</v>
-      </c>
-      <c r="E67" s="8" t="inlineStr">
+        <v>7.360000133514404</v>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -2413,9 +2413,9 @@
         <v>8</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>6.809999942779541</v>
-      </c>
-      <c r="E68" s="8" t="inlineStr">
+        <v>7.369999885559082</v>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -2441,9 +2441,9 @@
         <v>8</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>6.940000057220459</v>
-      </c>
-      <c r="E69" s="8" t="inlineStr">
+        <v>7.409999847412109</v>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -2469,16 +2469,16 @@
         <v>8</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>7.539999961853027</v>
-      </c>
-      <c r="E70" s="8" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="F70" s="8" t="inlineStr">
-        <is>
-          <t>A+</t>
+        <v>7.460000038146973</v>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -2497,16 +2497,16 @@
         <v>8</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>7.630000114440918</v>
-      </c>
-      <c r="E71" s="8" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="F71" s="8" t="inlineStr">
-        <is>
-          <t>A+</t>
+        <v>7.380000114440918</v>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -2525,16 +2525,16 @@
         <v>8</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>6.480000019073486</v>
-      </c>
-      <c r="E72" s="8" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="F72" s="5" t="inlineStr">
-        <is>
-          <t>A-</t>
+        <v>6.769999980926514</v>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -2553,16 +2553,16 @@
         <v>8</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>5.920000076293945</v>
-      </c>
-      <c r="E73" s="8" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="F73" s="5" t="inlineStr">
-        <is>
-          <t>A-</t>
+        <v>6.650000095367432</v>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -2581,16 +2581,16 @@
         <v>8</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>5.909999847412109</v>
-      </c>
-      <c r="E74" s="8" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="F74" s="5" t="inlineStr">
-        <is>
-          <t>A-</t>
+        <v>6.75</v>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -2609,16 +2609,16 @@
         <v>8</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>6.300000190734863</v>
-      </c>
-      <c r="E75" s="8" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="F75" s="5" t="inlineStr">
-        <is>
-          <t>A-</t>
+        <v>6.849999904632568</v>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -2637,14 +2637,14 @@
         <v>8</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="E76" s="8" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="F76" s="5" t="inlineStr">
+        <v>6.079999923706055</v>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="inlineStr">
         <is>
           <t>A-</t>
         </is>
@@ -2665,14 +2665,14 @@
         <v>8</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>5.679999828338623</v>
-      </c>
-      <c r="E77" s="8" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="F77" s="5" t="inlineStr">
+        <v>5.789999961853027</v>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
         <is>
           <t>A-</t>
         </is>
@@ -2693,14 +2693,14 @@
         <v>8</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>5.730000019073486</v>
-      </c>
-      <c r="E78" s="8" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="F78" s="5" t="inlineStr">
+        <v>5.880000114440918</v>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr">
         <is>
           <t>A-</t>
         </is>
@@ -2721,14 +2721,14 @@
         <v>8</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>6.190000057220459</v>
-      </c>
-      <c r="E79" s="8" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="F79" s="5" t="inlineStr">
+        <v>5.789999961853027</v>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
         <is>
           <t>A-</t>
         </is>
@@ -2749,16 +2749,16 @@
         <v>8</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>6.789999961853027</v>
-      </c>
-      <c r="E80" s="8" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="F80" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
+        <v>6.480000019073486</v>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>A-</t>
         </is>
       </c>
     </row>
@@ -2777,9 +2777,9 @@
         <v>8</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="E81" s="8" t="inlineStr">
+        <v>6.980000019073486</v>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -2805,16 +2805,16 @@
         <v>8</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>7.389999866485596</v>
-      </c>
-      <c r="E82" s="8" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="F82" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
+        <v>7.610000133514404</v>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -2833,9 +2833,9 @@
         <v>8</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="E83" s="8" t="inlineStr">
+        <v>7.489999771118164</v>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -2861,9 +2861,9 @@
         <v>8</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>6.739999771118164</v>
-      </c>
-      <c r="E84" s="8" t="inlineStr">
+        <v>6.690000057220459</v>
+      </c>
+      <c r="E84" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -2889,16 +2889,16 @@
         <v>8</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>7.789999961853027</v>
-      </c>
-      <c r="E85" s="8" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="F85" s="8" t="inlineStr">
-        <is>
-          <t>A+</t>
+        <v>6.630000114440918</v>
+      </c>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -2917,16 +2917,16 @@
         <v>8</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>7.869999885559082</v>
-      </c>
-      <c r="E86" s="8" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="F86" s="8" t="inlineStr">
-        <is>
-          <t>A+</t>
+        <v>6.630000114440918</v>
+      </c>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -2945,16 +2945,16 @@
         <v>8</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>6.260000228881836</v>
-      </c>
-      <c r="E87" s="8" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="F87" s="5" t="inlineStr">
-        <is>
-          <t>A-</t>
+        <v>6.730000019073486</v>
+      </c>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -2973,16 +2973,16 @@
         <v>9</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>9.229999542236328</v>
-      </c>
-      <c r="E88" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F88" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+        <v>8.479999542236328</v>
+      </c>
+      <c r="E88" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -3001,14 +3001,14 @@
         <v>9</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>8.460000038146973</v>
-      </c>
-      <c r="E89" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F89" s="8" t="inlineStr">
+        <v>7.53000020980835</v>
+      </c>
+      <c r="E89" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -3029,16 +3029,16 @@
         <v>9</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>8.760000228881836</v>
-      </c>
-      <c r="E90" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F90" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+        <v>8.039999961853027</v>
+      </c>
+      <c r="E90" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -3057,16 +3057,16 @@
         <v>9</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>8.689999580383301</v>
-      </c>
-      <c r="E91" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F91" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+        <v>7.96999979019165</v>
+      </c>
+      <c r="E91" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F91" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -3085,14 +3085,14 @@
         <v>9</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>8.460000038146973</v>
-      </c>
-      <c r="E92" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F92" s="8" t="inlineStr">
+        <v>7.820000171661377</v>
+      </c>
+      <c r="E92" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F92" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -3113,16 +3113,16 @@
         <v>9</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>8.689999580383301</v>
-      </c>
-      <c r="E93" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F93" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+        <v>8.239999771118164</v>
+      </c>
+      <c r="E93" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -3141,14 +3141,14 @@
         <v>9</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>8.149999618530273</v>
-      </c>
-      <c r="E94" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F94" s="8" t="inlineStr">
+        <v>8.460000038146973</v>
+      </c>
+      <c r="E94" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F94" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -3169,14 +3169,14 @@
         <v>9</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="E95" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F95" s="8" t="inlineStr">
+        <v>8.430000305175781</v>
+      </c>
+      <c r="E95" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F95" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -3197,16 +3197,16 @@
         <v>9</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>8.390000343322754</v>
-      </c>
-      <c r="E96" s="7" t="inlineStr">
+        <v>8.609999656677246</v>
+      </c>
+      <c r="E96" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
       </c>
       <c r="F96" s="8" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>AA-</t>
         </is>
       </c>
     </row>
@@ -3225,14 +3225,14 @@
         <v>9</v>
       </c>
       <c r="D97" s="3" t="n">
-        <v>8.810000419616699</v>
-      </c>
-      <c r="E97" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F97" s="7" t="inlineStr">
+        <v>9.039999961853027</v>
+      </c>
+      <c r="E97" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F97" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -3253,14 +3253,14 @@
         <v>9</v>
       </c>
       <c r="D98" s="3" t="n">
-        <v>8.649999618530273</v>
-      </c>
-      <c r="E98" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F98" s="7" t="inlineStr">
+        <v>8.5</v>
+      </c>
+      <c r="E98" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F98" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -3281,14 +3281,14 @@
         <v>9</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>7.96999979019165</v>
-      </c>
-      <c r="E99" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F99" s="8" t="inlineStr">
+        <v>7.670000076293945</v>
+      </c>
+      <c r="E99" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F99" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -3309,16 +3309,16 @@
         <v>9</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>8.529999732971191</v>
-      </c>
-      <c r="E100" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F100" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+        <v>8.130000114440918</v>
+      </c>
+      <c r="E100" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F100" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -3337,16 +3337,16 @@
         <v>9</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>8.760000228881836</v>
-      </c>
-      <c r="E101" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F101" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+        <v>8.300000190734863</v>
+      </c>
+      <c r="E101" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -3365,14 +3365,14 @@
         <v>9</v>
       </c>
       <c r="D102" s="3" t="n">
-        <v>8.800000190734863</v>
-      </c>
-      <c r="E102" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F102" s="7" t="inlineStr">
+        <v>8.689999580383301</v>
+      </c>
+      <c r="E102" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F102" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -3393,14 +3393,14 @@
         <v>9</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>8.800000190734863</v>
-      </c>
-      <c r="E103" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F103" s="7" t="inlineStr">
+        <v>8.689999580383301</v>
+      </c>
+      <c r="E103" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F103" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -3421,14 +3421,14 @@
         <v>9</v>
       </c>
       <c r="D104" s="3" t="n">
-        <v>8.729999542236328</v>
-      </c>
-      <c r="E104" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F104" s="7" t="inlineStr">
+        <v>8.619999885559082</v>
+      </c>
+      <c r="E104" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F104" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -3449,14 +3449,14 @@
         <v>9</v>
       </c>
       <c r="D105" s="3" t="n">
-        <v>8.779999732971191</v>
-      </c>
-      <c r="E105" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F105" s="7" t="inlineStr">
+        <v>8.819999694824219</v>
+      </c>
+      <c r="E105" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F105" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -3477,14 +3477,14 @@
         <v>9</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>8.880000114440918</v>
-      </c>
-      <c r="E106" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F106" s="7" t="inlineStr">
+        <v>8.770000457763672</v>
+      </c>
+      <c r="E106" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F106" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -3505,14 +3505,14 @@
         <v>9</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>8.800000190734863</v>
-      </c>
-      <c r="E107" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F107" s="7" t="inlineStr">
+        <v>8.520000457763672</v>
+      </c>
+      <c r="E107" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F107" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -3533,16 +3533,16 @@
         <v>9</v>
       </c>
       <c r="D108" s="3" t="n">
-        <v>8.800000190734863</v>
-      </c>
-      <c r="E108" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F108" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+        <v>8.399999618530273</v>
+      </c>
+      <c r="E108" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F108" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -3561,16 +3561,16 @@
         <v>9</v>
       </c>
       <c r="D109" s="3" t="n">
-        <v>8.760000228881836</v>
-      </c>
-      <c r="E109" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F109" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+        <v>8.319999694824219</v>
+      </c>
+      <c r="E109" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F109" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -3589,16 +3589,16 @@
         <v>9</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>8.579999923706055</v>
-      </c>
-      <c r="E110" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F110" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+        <v>8.369999885559082</v>
+      </c>
+      <c r="E110" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F110" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -3617,16 +3617,16 @@
         <v>8</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>8.300000190734863</v>
-      </c>
-      <c r="E111" s="8" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="F111" s="8" t="inlineStr">
-        <is>
-          <t>A+</t>
+        <v>7.320000171661377</v>
+      </c>
+      <c r="E111" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -3645,16 +3645,16 @@
         <v>8</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>8.800000190734863</v>
-      </c>
-      <c r="E112" s="8" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="F112" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+        <v>7.590000152587891</v>
+      </c>
+      <c r="E112" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="F112" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -3673,16 +3673,16 @@
         <v>8</v>
       </c>
       <c r="D113" s="3" t="n">
-        <v>8.609999656677246</v>
-      </c>
-      <c r="E113" s="8" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="F113" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+        <v>7.519999980926514</v>
+      </c>
+      <c r="E113" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="F113" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -3701,14 +3701,14 @@
         <v>8</v>
       </c>
       <c r="D114" s="3" t="n">
-        <v>8.300000190734863</v>
-      </c>
-      <c r="E114" s="8" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="F114" s="8" t="inlineStr">
+        <v>7.570000171661377</v>
+      </c>
+      <c r="E114" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="F114" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -3729,9 +3729,9 @@
         <v>8</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E115" s="8" t="inlineStr">
+        <v>6.840000152587891</v>
+      </c>
+      <c r="E115" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -3757,9 +3757,9 @@
         <v>8</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>7.489999771118164</v>
-      </c>
-      <c r="E116" s="8" t="inlineStr">
+        <v>6.889999866485596</v>
+      </c>
+      <c r="E116" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -3785,16 +3785,16 @@
         <v>8</v>
       </c>
       <c r="D117" s="3" t="n">
-        <v>8.140000343322754</v>
-      </c>
-      <c r="E117" s="8" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="F117" s="8" t="inlineStr">
-        <is>
-          <t>A+</t>
+        <v>7.260000228881836</v>
+      </c>
+      <c r="E117" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -3813,14 +3813,14 @@
         <v>8</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>8.220000267028809</v>
-      </c>
-      <c r="E118" s="8" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="F118" s="8" t="inlineStr">
+        <v>7.639999866485596</v>
+      </c>
+      <c r="E118" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="F118" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -3841,14 +3841,14 @@
         <v>8</v>
       </c>
       <c r="D119" s="3" t="n">
-        <v>8.060000419616699</v>
-      </c>
-      <c r="E119" s="8" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="F119" s="8" t="inlineStr">
+        <v>7.789999961853027</v>
+      </c>
+      <c r="E119" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="F119" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -3869,9 +3869,9 @@
         <v>8</v>
       </c>
       <c r="D120" s="3" t="n">
-        <v>7.139999866485596</v>
-      </c>
-      <c r="E120" s="8" t="inlineStr">
+        <v>7.03000020980835</v>
+      </c>
+      <c r="E120" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -3897,16 +3897,16 @@
         <v>8</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>6.489999771118164</v>
-      </c>
-      <c r="E121" s="8" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="F121" s="5" t="inlineStr">
-        <is>
-          <t>A-</t>
+        <v>6.730000019073486</v>
+      </c>
+      <c r="E121" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -3925,9 +3925,9 @@
         <v>8</v>
       </c>
       <c r="D122" s="3" t="n">
-        <v>6.570000171661377</v>
-      </c>
-      <c r="E122" s="8" t="inlineStr">
+        <v>6.920000076293945</v>
+      </c>
+      <c r="E122" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -3953,9 +3953,9 @@
         <v>8</v>
       </c>
       <c r="D123" s="3" t="n">
-        <v>7.010000228881836</v>
-      </c>
-      <c r="E123" s="8" t="inlineStr">
+        <v>7.019999980926514</v>
+      </c>
+      <c r="E123" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -3981,16 +3981,16 @@
         <v>8</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>7.130000114440918</v>
-      </c>
-      <c r="E124" s="8" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="F124" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
+        <v>7.570000171661377</v>
+      </c>
+      <c r="E124" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="F124" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -4009,14 +4009,14 @@
         <v>8</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>8.640000343322754</v>
-      </c>
-      <c r="E125" s="8" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="F125" s="7" t="inlineStr">
+        <v>8.510000228881836</v>
+      </c>
+      <c r="E125" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="F125" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -4037,14 +4037,14 @@
         <v>7</v>
       </c>
       <c r="D126" s="3" t="n">
-        <v>6.28000020980835</v>
+        <v>5.889999866485596</v>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F126" s="5" t="inlineStr">
+      <c r="F126" s="7" t="inlineStr">
         <is>
           <t>A-</t>
         </is>
@@ -4065,14 +4065,14 @@
         <v>7</v>
       </c>
       <c r="D127" s="3" t="n">
-        <v>6.179999828338623</v>
+        <v>5.829999923706055</v>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F127" s="5" t="inlineStr">
+      <c r="F127" s="7" t="inlineStr">
         <is>
           <t>A-</t>
         </is>
@@ -4093,14 +4093,14 @@
         <v>7</v>
       </c>
       <c r="D128" s="3" t="n">
-        <v>6.440000057220459</v>
+        <v>6.409999847412109</v>
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F128" s="5" t="inlineStr">
+      <c r="F128" s="7" t="inlineStr">
         <is>
           <t>A-</t>
         </is>
@@ -4121,14 +4121,14 @@
         <v>7</v>
       </c>
       <c r="D129" s="3" t="n">
-        <v>6.039999961853027</v>
+        <v>5.880000114440918</v>
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F129" s="5" t="inlineStr">
+      <c r="F129" s="7" t="inlineStr">
         <is>
           <t>A-</t>
         </is>
@@ -4149,14 +4149,14 @@
         <v>7</v>
       </c>
       <c r="D130" s="3" t="n">
-        <v>6.360000133514404</v>
+        <v>5.980000019073486</v>
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F130" s="5" t="inlineStr">
+      <c r="F130" s="7" t="inlineStr">
         <is>
           <t>A-</t>
         </is>
@@ -4177,14 +4177,14 @@
         <v>7</v>
       </c>
       <c r="D131" s="3" t="n">
-        <v>6.119999885559082</v>
+        <v>5.860000133514404</v>
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F131" s="5" t="inlineStr">
+      <c r="F131" s="7" t="inlineStr">
         <is>
           <t>A-</t>
         </is>
@@ -4205,14 +4205,14 @@
         <v>7</v>
       </c>
       <c r="D132" s="3" t="n">
-        <v>6.039999961853027</v>
+        <v>5.599999904632568</v>
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F132" s="5" t="inlineStr">
+      <c r="F132" s="7" t="inlineStr">
         <is>
           <t>A-</t>
         </is>
@@ -4233,16 +4233,16 @@
         <v>7</v>
       </c>
       <c r="D133" s="3" t="n">
-        <v>6.139999866485596</v>
+        <v>5.409999847412109</v>
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F133" s="5" t="inlineStr">
-        <is>
-          <t>A-</t>
+      <c r="F133" s="6" t="inlineStr">
+        <is>
+          <t>BBB+</t>
         </is>
       </c>
     </row>
@@ -4261,16 +4261,16 @@
         <v>7</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>5.869999885559082</v>
+        <v>5.019999980926514</v>
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F134" s="5" t="inlineStr">
-        <is>
-          <t>A-</t>
+      <c r="F134" s="6" t="inlineStr">
+        <is>
+          <t>BBB+</t>
         </is>
       </c>
     </row>
@@ -4289,16 +4289,16 @@
         <v>7</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>5.800000190734863</v>
+        <v>5.010000228881836</v>
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F135" s="5" t="inlineStr">
-        <is>
-          <t>A-</t>
+      <c r="F135" s="6" t="inlineStr">
+        <is>
+          <t>BBB+</t>
         </is>
       </c>
     </row>
@@ -4317,16 +4317,16 @@
         <v>7</v>
       </c>
       <c r="D136" s="3" t="n">
-        <v>5.730000019073486</v>
+        <v>5.340000152587891</v>
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F136" s="5" t="inlineStr">
-        <is>
-          <t>A-</t>
+      <c r="F136" s="6" t="inlineStr">
+        <is>
+          <t>BBB+</t>
         </is>
       </c>
     </row>
@@ -4345,16 +4345,16 @@
         <v>7</v>
       </c>
       <c r="D137" s="3" t="n">
-        <v>5.940000057220459</v>
+        <v>6.900000095367432</v>
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F137" s="5" t="inlineStr">
-        <is>
-          <t>A-</t>
+      <c r="F137" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -4373,16 +4373,16 @@
         <v>7</v>
       </c>
       <c r="D138" s="3" t="n">
-        <v>5.260000228881836</v>
+        <v>7.730000019073486</v>
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F138" s="6" t="inlineStr">
-        <is>
-          <t>BBB+</t>
+      <c r="F138" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -4401,16 +4401,16 @@
         <v>7</v>
       </c>
       <c r="D139" s="3" t="n">
-        <v>5.460000038146973</v>
+        <v>6.059999942779541</v>
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F139" s="6" t="inlineStr">
-        <is>
-          <t>BBB+</t>
+      <c r="F139" s="7" t="inlineStr">
+        <is>
+          <t>A-</t>
         </is>
       </c>
     </row>
@@ -4429,16 +4429,16 @@
         <v>7</v>
       </c>
       <c r="D140" s="3" t="n">
-        <v>5.71999979019165</v>
+        <v>4.769999980926514</v>
       </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F140" s="5" t="inlineStr">
-        <is>
-          <t>A-</t>
+      <c r="F140" s="6" t="inlineStr">
+        <is>
+          <t>BBB+</t>
         </is>
       </c>
     </row>
@@ -4457,16 +4457,16 @@
         <v>7</v>
       </c>
       <c r="D141" s="3" t="n">
-        <v>5.78000020980835</v>
+        <v>5.03000020980835</v>
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F141" s="5" t="inlineStr">
-        <is>
-          <t>A-</t>
+      <c r="F141" s="6" t="inlineStr">
+        <is>
+          <t>BBB+</t>
         </is>
       </c>
     </row>
@@ -4485,16 +4485,16 @@
         <v>7</v>
       </c>
       <c r="D142" s="3" t="n">
-        <v>5.769999980926514</v>
+        <v>5.309999942779541</v>
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F142" s="5" t="inlineStr">
-        <is>
-          <t>A-</t>
+      <c r="F142" s="6" t="inlineStr">
+        <is>
+          <t>BBB+</t>
         </is>
       </c>
     </row>
@@ -4513,14 +4513,14 @@
         <v>7</v>
       </c>
       <c r="D143" s="3" t="n">
-        <v>5.860000133514404</v>
+        <v>6.179999828338623</v>
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F143" s="5" t="inlineStr">
+      <c r="F143" s="7" t="inlineStr">
         <is>
           <t>A-</t>
         </is>
@@ -4541,16 +4541,16 @@
         <v>7</v>
       </c>
       <c r="D144" s="3" t="n">
-        <v>5.869999885559082</v>
+        <v>7.099999904632568</v>
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F144" s="5" t="inlineStr">
-        <is>
-          <t>A-</t>
+      <c r="F144" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -4569,14 +4569,14 @@
         <v>7</v>
       </c>
       <c r="D145" s="3" t="n">
-        <v>6.050000190734863</v>
+        <v>6.059999942779541</v>
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F145" s="5" t="inlineStr">
+      <c r="F145" s="7" t="inlineStr">
         <is>
           <t>A-</t>
         </is>
@@ -4604,7 +4604,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F146" s="5" t="inlineStr">
+      <c r="F146" s="7" t="inlineStr">
         <is>
           <t>A-</t>
         </is>
@@ -4625,14 +4625,14 @@
         <v>7</v>
       </c>
       <c r="D147" s="3" t="n">
-        <v>5.820000171661377</v>
+        <v>5.949999809265137</v>
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F147" s="5" t="inlineStr">
+      <c r="F147" s="7" t="inlineStr">
         <is>
           <t>A-</t>
         </is>
@@ -4653,14 +4653,14 @@
         <v>7</v>
       </c>
       <c r="D148" s="3" t="n">
-        <v>5.829999923706055</v>
+        <v>6.260000228881836</v>
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F148" s="5" t="inlineStr">
+      <c r="F148" s="7" t="inlineStr">
         <is>
           <t>A-</t>
         </is>
@@ -4709,7 +4709,7 @@
         <v>7</v>
       </c>
       <c r="D150" s="3" t="n">
-        <v>7.369999885559082</v>
+        <v>7.139999866485596</v>
       </c>
       <c r="E150" s="4" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>7</v>
       </c>
       <c r="D151" s="3" t="n">
-        <v>6.71999979019165</v>
+        <v>6.820000171661377</v>
       </c>
       <c r="E151" s="4" t="inlineStr">
         <is>
@@ -4765,16 +4765,16 @@
         <v>7</v>
       </c>
       <c r="D152" s="3" t="n">
-        <v>7.309999942779541</v>
+        <v>7.539999961853027</v>
       </c>
       <c r="E152" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F152" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="F152" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -4793,16 +4793,16 @@
         <v>7</v>
       </c>
       <c r="D153" s="3" t="n">
-        <v>7.389999866485596</v>
+        <v>7.820000171661377</v>
       </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F153" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="F153" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -4821,16 +4821,16 @@
         <v>7</v>
       </c>
       <c r="D154" s="3" t="n">
-        <v>7.480000019073486</v>
+        <v>7.800000190734863</v>
       </c>
       <c r="E154" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F154" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="F154" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -4849,16 +4849,16 @@
         <v>9</v>
       </c>
       <c r="D155" s="3" t="n">
-        <v>8.189999580383301</v>
-      </c>
-      <c r="E155" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F155" s="8" t="inlineStr">
-        <is>
-          <t>A+</t>
+        <v>7.349999904632568</v>
+      </c>
+      <c r="E155" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F155" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -4877,16 +4877,16 @@
         <v>9</v>
       </c>
       <c r="D156" s="3" t="n">
-        <v>8.560000419616699</v>
-      </c>
-      <c r="E156" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F156" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+        <v>7.78000020980835</v>
+      </c>
+      <c r="E156" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F156" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -4905,14 +4905,14 @@
         <v>9</v>
       </c>
       <c r="D157" s="3" t="n">
-        <v>8.390000343322754</v>
-      </c>
-      <c r="E157" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F157" s="8" t="inlineStr">
+        <v>7.599999904632568</v>
+      </c>
+      <c r="E157" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F157" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -4933,14 +4933,14 @@
         <v>9</v>
       </c>
       <c r="D158" s="3" t="n">
-        <v>8.449999809265137</v>
-      </c>
-      <c r="E158" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F158" s="8" t="inlineStr">
+        <v>7.820000171661377</v>
+      </c>
+      <c r="E158" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F158" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -4961,14 +4961,14 @@
         <v>10</v>
       </c>
       <c r="D159" s="3" t="n">
-        <v>9.199999809265137</v>
+        <v>8.920000076293945</v>
       </c>
       <c r="E159" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F159" s="7" t="inlineStr">
+      <c r="F159" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -4989,16 +4989,16 @@
         <v>10</v>
       </c>
       <c r="D160" s="3" t="n">
-        <v>8.989999771118164</v>
+        <v>8.380000114440918</v>
       </c>
       <c r="E160" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F160" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+      <c r="F160" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -5017,16 +5017,16 @@
         <v>10</v>
       </c>
       <c r="D161" s="3" t="n">
-        <v>9.149999618530273</v>
+        <v>8.100000381469727</v>
       </c>
       <c r="E161" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F161" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+      <c r="F161" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -5045,16 +5045,16 @@
         <v>10</v>
       </c>
       <c r="D162" s="3" t="n">
-        <v>9.239999771118164</v>
+        <v>8.479999542236328</v>
       </c>
       <c r="E162" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F162" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+      <c r="F162" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -5073,14 +5073,14 @@
         <v>10</v>
       </c>
       <c r="D163" s="3" t="n">
-        <v>9.229999542236328</v>
+        <v>8.670000076293945</v>
       </c>
       <c r="E163" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F163" s="7" t="inlineStr">
+      <c r="F163" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -5101,16 +5101,16 @@
         <v>10</v>
       </c>
       <c r="D164" s="3" t="n">
-        <v>9.479999542236328</v>
+        <v>7.059999942779541</v>
       </c>
       <c r="E164" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F164" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+      <c r="F164" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -5129,14 +5129,14 @@
         <v>10</v>
       </c>
       <c r="D165" s="3" t="n">
-        <v>9.270000457763672</v>
+        <v>8.970000267028809</v>
       </c>
       <c r="E165" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F165" s="7" t="inlineStr">
+      <c r="F165" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -5157,14 +5157,14 @@
         <v>10</v>
       </c>
       <c r="D166" s="3" t="n">
-        <v>9.329999923706055</v>
+        <v>9.020000457763672</v>
       </c>
       <c r="E166" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F166" s="7" t="inlineStr">
+      <c r="F166" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -5185,14 +5185,14 @@
         <v>10</v>
       </c>
       <c r="D167" s="3" t="n">
-        <v>9.439999580383301</v>
+        <v>9</v>
       </c>
       <c r="E167" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F167" s="7" t="inlineStr">
+      <c r="F167" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -5213,14 +5213,14 @@
         <v>10</v>
       </c>
       <c r="D168" s="3" t="n">
-        <v>9.399999618530273</v>
+        <v>9</v>
       </c>
       <c r="E168" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F168" s="7" t="inlineStr">
+      <c r="F168" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -5241,16 +5241,16 @@
         <v>10</v>
       </c>
       <c r="D169" s="3" t="n">
-        <v>9.090000152587891</v>
+        <v>8.310000419616699</v>
       </c>
       <c r="E169" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F169" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+      <c r="F169" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -5269,16 +5269,16 @@
         <v>10</v>
       </c>
       <c r="D170" s="3" t="n">
-        <v>9.060000419616699</v>
+        <v>7.829999923706055</v>
       </c>
       <c r="E170" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F170" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+      <c r="F170" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -5297,16 +5297,16 @@
         <v>10</v>
       </c>
       <c r="D171" s="3" t="n">
-        <v>9.159999847412109</v>
+        <v>8.069999694824219</v>
       </c>
       <c r="E171" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F171" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+      <c r="F171" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -5325,14 +5325,14 @@
         <v>10</v>
       </c>
       <c r="D172" s="3" t="n">
-        <v>9.350000381469727</v>
+        <v>8.909999847412109</v>
       </c>
       <c r="E172" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F172" s="7" t="inlineStr">
+      <c r="F172" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -5353,14 +5353,14 @@
         <v>10</v>
       </c>
       <c r="D173" s="3" t="n">
-        <v>9.470000267028809</v>
+        <v>8.869999885559082</v>
       </c>
       <c r="E173" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F173" s="7" t="inlineStr">
+      <c r="F173" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -5381,14 +5381,14 @@
         <v>10</v>
       </c>
       <c r="D174" s="3" t="n">
-        <v>9.380000114440918</v>
+        <v>8.800000190734863</v>
       </c>
       <c r="E174" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F174" s="7" t="inlineStr">
+      <c r="F174" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -5409,14 +5409,14 @@
         <v>10</v>
       </c>
       <c r="D175" s="3" t="n">
-        <v>9.310000419616699</v>
+        <v>8.680000305175781</v>
       </c>
       <c r="E175" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F175" s="7" t="inlineStr">
+      <c r="F175" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -5437,14 +5437,14 @@
         <v>10</v>
       </c>
       <c r="D176" s="3" t="n">
-        <v>9.369999885559082</v>
+        <v>8.720000267028809</v>
       </c>
       <c r="E176" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F176" s="7" t="inlineStr">
+      <c r="F176" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -5465,14 +5465,14 @@
         <v>10</v>
       </c>
       <c r="D177" s="3" t="n">
-        <v>9.479999542236328</v>
+        <v>8.710000038146973</v>
       </c>
       <c r="E177" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F177" s="7" t="inlineStr">
+      <c r="F177" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -5493,16 +5493,16 @@
         <v>10</v>
       </c>
       <c r="D178" s="3" t="n">
-        <v>9.569999694824219</v>
+        <v>9.060000419616699</v>
       </c>
       <c r="E178" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F178" s="9" t="inlineStr">
-        <is>
-          <t>AA</t>
+      <c r="F178" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
         </is>
       </c>
     </row>
@@ -5521,16 +5521,16 @@
         <v>10</v>
       </c>
       <c r="D179" s="3" t="n">
-        <v>9.550000190734863</v>
+        <v>9.149999618530273</v>
       </c>
       <c r="E179" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F179" s="9" t="inlineStr">
-        <is>
-          <t>AA</t>
+      <c r="F179" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
         </is>
       </c>
     </row>
@@ -5549,14 +5549,14 @@
         <v>10</v>
       </c>
       <c r="D180" s="3" t="n">
-        <v>9.390000343322754</v>
+        <v>9.069999694824219</v>
       </c>
       <c r="E180" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F180" s="7" t="inlineStr">
+      <c r="F180" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -5577,16 +5577,16 @@
         <v>9</v>
       </c>
       <c r="D181" s="3" t="n">
-        <v>7.099999904632568</v>
-      </c>
-      <c r="E181" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F181" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
+        <v>6.489999771118164</v>
+      </c>
+      <c r="E181" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F181" s="7" t="inlineStr">
+        <is>
+          <t>A-</t>
         </is>
       </c>
     </row>
@@ -5605,9 +5605,9 @@
         <v>9</v>
       </c>
       <c r="D182" s="3" t="n">
-        <v>7.210000038146973</v>
-      </c>
-      <c r="E182" s="7" t="inlineStr">
+        <v>6.599999904632568</v>
+      </c>
+      <c r="E182" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -5633,16 +5633,16 @@
         <v>10</v>
       </c>
       <c r="D183" s="3" t="n">
-        <v>8.960000038146973</v>
+        <v>7.920000076293945</v>
       </c>
       <c r="E183" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F183" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+      <c r="F183" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -5661,16 +5661,16 @@
         <v>10</v>
       </c>
       <c r="D184" s="3" t="n">
-        <v>8.659999847412109</v>
+        <v>6.920000076293945</v>
       </c>
       <c r="E184" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F184" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+      <c r="F184" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -5689,16 +5689,16 @@
         <v>10</v>
       </c>
       <c r="D185" s="3" t="n">
-        <v>9.050000190734863</v>
+        <v>8.470000267028809</v>
       </c>
       <c r="E185" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F185" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+      <c r="F185" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -5717,14 +5717,14 @@
         <v>10</v>
       </c>
       <c r="D186" s="3" t="n">
-        <v>9.060000419616699</v>
+        <v>8.869999885559082</v>
       </c>
       <c r="E186" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F186" s="7" t="inlineStr">
+      <c r="F186" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -5745,14 +5745,14 @@
         <v>10</v>
       </c>
       <c r="D187" s="3" t="n">
-        <v>9.260000228881836</v>
+        <v>9.100000381469727</v>
       </c>
       <c r="E187" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F187" s="7" t="inlineStr">
+      <c r="F187" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -5773,14 +5773,14 @@
         <v>10</v>
       </c>
       <c r="D188" s="3" t="n">
-        <v>8.640000343322754</v>
+        <v>8.789999961853027</v>
       </c>
       <c r="E188" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F188" s="7" t="inlineStr">
+      <c r="F188" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -5801,14 +5801,14 @@
         <v>10</v>
       </c>
       <c r="D189" s="3" t="n">
-        <v>8.640000343322754</v>
+        <v>8.920000076293945</v>
       </c>
       <c r="E189" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F189" s="7" t="inlineStr">
+      <c r="F189" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -5829,14 +5829,14 @@
         <v>10</v>
       </c>
       <c r="D190" s="3" t="n">
-        <v>9.029999732971191</v>
+        <v>8.960000038146973</v>
       </c>
       <c r="E190" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F190" s="7" t="inlineStr">
+      <c r="F190" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -5857,14 +5857,14 @@
         <v>10</v>
       </c>
       <c r="D191" s="3" t="n">
-        <v>9.079999923706055</v>
+        <v>9.029999732971191</v>
       </c>
       <c r="E191" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F191" s="7" t="inlineStr">
+      <c r="F191" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -5885,14 +5885,14 @@
         <v>10</v>
       </c>
       <c r="D192" s="3" t="n">
-        <v>8.960000038146973</v>
+        <v>8.640000343322754</v>
       </c>
       <c r="E192" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F192" s="7" t="inlineStr">
+      <c r="F192" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -5913,14 +5913,14 @@
         <v>10</v>
       </c>
       <c r="D193" s="3" t="n">
-        <v>9.020000457763672</v>
+        <v>8.590000152587891</v>
       </c>
       <c r="E193" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F193" s="7" t="inlineStr">
+      <c r="F193" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -5941,14 +5941,14 @@
         <v>10</v>
       </c>
       <c r="D194" s="3" t="n">
-        <v>9.369999885559082</v>
+        <v>9.449999809265137</v>
       </c>
       <c r="E194" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F194" s="7" t="inlineStr">
+      <c r="F194" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -5969,7 +5969,7 @@
         <v>10</v>
       </c>
       <c r="D195" s="3" t="n">
-        <v>9.539999961853027</v>
+        <v>9.930000305175781</v>
       </c>
       <c r="E195" s="9" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>10</v>
       </c>
       <c r="D196" s="3" t="n">
-        <v>9.520000457763672</v>
+        <v>9.659999847412109</v>
       </c>
       <c r="E196" s="9" t="inlineStr">
         <is>
@@ -6032,7 +6032,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F197" s="7" t="inlineStr">
+      <c r="F197" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -6053,14 +6053,14 @@
         <v>10</v>
       </c>
       <c r="D198" s="3" t="n">
-        <v>9.130000114440918</v>
+        <v>8.800000190734863</v>
       </c>
       <c r="E198" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F198" s="7" t="inlineStr">
+      <c r="F198" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -6081,14 +6081,14 @@
         <v>10</v>
       </c>
       <c r="D199" s="3" t="n">
-        <v>9.060000419616699</v>
+        <v>9.020000457763672</v>
       </c>
       <c r="E199" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F199" s="7" t="inlineStr">
+      <c r="F199" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -6109,16 +6109,16 @@
         <v>10</v>
       </c>
       <c r="D200" s="3" t="n">
-        <v>7.28000020980835</v>
+        <v>8.609999656677246</v>
       </c>
       <c r="E200" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F200" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="F200" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
         </is>
       </c>
     </row>
@@ -6137,16 +6137,16 @@
         <v>10</v>
       </c>
       <c r="D201" s="3" t="n">
-        <v>9.069999694824219</v>
+        <v>8.329999923706055</v>
       </c>
       <c r="E201" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F201" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+      <c r="F201" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -6165,16 +6165,16 @@
         <v>10</v>
       </c>
       <c r="D202" s="3" t="n">
-        <v>9.199999809265137</v>
+        <v>8.470000267028809</v>
       </c>
       <c r="E202" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F202" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+      <c r="F202" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -6193,16 +6193,16 @@
         <v>10</v>
       </c>
       <c r="D203" s="3" t="n">
-        <v>8.840000152587891</v>
+        <v>8.390000343322754</v>
       </c>
       <c r="E203" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F203" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+      <c r="F203" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -6221,16 +6221,16 @@
         <v>10</v>
       </c>
       <c r="D204" s="3" t="n">
-        <v>9.199999809265137</v>
+        <v>8.350000381469727</v>
       </c>
       <c r="E204" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F204" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+      <c r="F204" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -6249,14 +6249,14 @@
         <v>10</v>
       </c>
       <c r="D205" s="3" t="n">
-        <v>9.340000152587891</v>
+        <v>8.529999732971191</v>
       </c>
       <c r="E205" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F205" s="7" t="inlineStr">
+      <c r="F205" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -6277,9 +6277,9 @@
         <v>8</v>
       </c>
       <c r="D206" s="3" t="n">
-        <v>7.329999923706055</v>
-      </c>
-      <c r="E206" s="8" t="inlineStr">
+        <v>6.980000019073486</v>
+      </c>
+      <c r="E206" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -6305,9 +6305,9 @@
         <v>8</v>
       </c>
       <c r="D207" s="3" t="n">
-        <v>7.369999885559082</v>
-      </c>
-      <c r="E207" s="8" t="inlineStr">
+        <v>7.179999828338623</v>
+      </c>
+      <c r="E207" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -6333,9 +6333,9 @@
         <v>8</v>
       </c>
       <c r="D208" s="3" t="n">
-        <v>7.210000038146973</v>
-      </c>
-      <c r="E208" s="8" t="inlineStr">
+        <v>7.090000152587891</v>
+      </c>
+      <c r="E208" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -6361,16 +6361,16 @@
         <v>9</v>
       </c>
       <c r="D209" s="3" t="n">
-        <v>7.03000020980835</v>
-      </c>
-      <c r="E209" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F209" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
+        <v>7.949999809265137</v>
+      </c>
+      <c r="E209" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F209" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -6389,14 +6389,14 @@
         <v>9</v>
       </c>
       <c r="D210" s="3" t="n">
-        <v>8.170000076293945</v>
-      </c>
-      <c r="E210" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F210" s="8" t="inlineStr">
+        <v>7.690000057220459</v>
+      </c>
+      <c r="E210" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F210" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -6417,16 +6417,16 @@
         <v>9</v>
       </c>
       <c r="D211" s="3" t="n">
-        <v>8.720000267028809</v>
-      </c>
-      <c r="E211" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F211" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+        <v>7.21999979019165</v>
+      </c>
+      <c r="E211" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F211" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -6445,16 +6445,16 @@
         <v>9</v>
       </c>
       <c r="D212" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="E212" s="7" t="inlineStr">
+        <v>7.510000228881836</v>
+      </c>
+      <c r="E212" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
       </c>
       <c r="F212" s="5" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -6473,16 +6473,16 @@
         <v>9</v>
       </c>
       <c r="D213" s="3" t="n">
-        <v>7.96999979019165</v>
-      </c>
-      <c r="E213" s="7" t="inlineStr">
+        <v>8.600000381469727</v>
+      </c>
+      <c r="E213" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
       </c>
       <c r="F213" s="8" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>AA-</t>
         </is>
       </c>
     </row>
@@ -6501,16 +6501,16 @@
         <v>9</v>
       </c>
       <c r="D214" s="3" t="n">
-        <v>8.090000152587891</v>
-      </c>
-      <c r="E214" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F214" s="8" t="inlineStr">
-        <is>
-          <t>A+</t>
+        <v>6.650000095367432</v>
+      </c>
+      <c r="E214" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F214" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -6529,16 +6529,16 @@
         <v>9</v>
       </c>
       <c r="D215" s="3" t="n">
-        <v>8.270000457763672</v>
-      </c>
-      <c r="E215" s="7" t="inlineStr">
+        <v>8.689999580383301</v>
+      </c>
+      <c r="E215" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
       </c>
       <c r="F215" s="8" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>AA-</t>
         </is>
       </c>
     </row>
@@ -6557,14 +6557,14 @@
         <v>9</v>
       </c>
       <c r="D216" s="3" t="n">
-        <v>8.130000114440918</v>
-      </c>
-      <c r="E216" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F216" s="8" t="inlineStr">
+        <v>8.319999694824219</v>
+      </c>
+      <c r="E216" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F216" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -6585,14 +6585,14 @@
         <v>9</v>
       </c>
       <c r="D217" s="3" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="E217" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F217" s="8" t="inlineStr">
+        <v>7.949999809265137</v>
+      </c>
+      <c r="E217" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F217" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -6613,14 +6613,14 @@
         <v>9</v>
       </c>
       <c r="D218" s="3" t="n">
-        <v>8.210000038146973</v>
-      </c>
-      <c r="E218" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F218" s="8" t="inlineStr">
+        <v>7.690000057220459</v>
+      </c>
+      <c r="E218" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F218" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -6641,14 +6641,14 @@
         <v>9</v>
       </c>
       <c r="D219" s="3" t="n">
-        <v>8.149999618530273</v>
-      </c>
-      <c r="E219" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F219" s="8" t="inlineStr">
+        <v>7.809999942779541</v>
+      </c>
+      <c r="E219" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F219" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -6669,14 +6669,14 @@
         <v>9</v>
       </c>
       <c r="D220" s="3" t="n">
-        <v>8.279999732971191</v>
-      </c>
-      <c r="E220" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F220" s="8" t="inlineStr">
+        <v>7.929999828338623</v>
+      </c>
+      <c r="E220" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F220" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -6697,16 +6697,16 @@
         <v>9</v>
       </c>
       <c r="D221" s="3" t="n">
-        <v>8.590000152587891</v>
-      </c>
-      <c r="E221" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F221" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+        <v>8.319999694824219</v>
+      </c>
+      <c r="E221" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F221" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -6725,14 +6725,14 @@
         <v>9</v>
       </c>
       <c r="D222" s="3" t="n">
-        <v>8.689999580383301</v>
-      </c>
-      <c r="E222" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F222" s="7" t="inlineStr">
+        <v>8.840000152587891</v>
+      </c>
+      <c r="E222" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F222" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -6753,14 +6753,14 @@
         <v>9</v>
       </c>
       <c r="D223" s="3" t="n">
-        <v>8.789999961853027</v>
-      </c>
-      <c r="E223" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F223" s="7" t="inlineStr">
+        <v>8.810000419616699</v>
+      </c>
+      <c r="E223" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F223" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -6781,16 +6781,16 @@
         <v>9</v>
       </c>
       <c r="D224" s="3" t="n">
-        <v>8.590000152587891</v>
-      </c>
-      <c r="E224" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F224" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+        <v>8.289999961853027</v>
+      </c>
+      <c r="E224" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F224" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -6809,14 +6809,14 @@
         <v>9</v>
       </c>
       <c r="D225" s="3" t="n">
-        <v>8.279999732971191</v>
-      </c>
-      <c r="E225" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F225" s="8" t="inlineStr">
+        <v>7.630000114440918</v>
+      </c>
+      <c r="E225" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F225" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -6837,14 +6837,14 @@
         <v>9</v>
       </c>
       <c r="D226" s="3" t="n">
-        <v>8.279999732971191</v>
-      </c>
-      <c r="E226" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F226" s="8" t="inlineStr">
+        <v>7.630000114440918</v>
+      </c>
+      <c r="E226" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F226" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -6865,16 +6865,16 @@
         <v>9</v>
       </c>
       <c r="D227" s="3" t="n">
-        <v>8.210000038146973</v>
-      </c>
-      <c r="E227" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F227" s="8" t="inlineStr">
-        <is>
-          <t>A+</t>
+        <v>7.369999885559082</v>
+      </c>
+      <c r="E227" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F227" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -6893,16 +6893,16 @@
         <v>9</v>
       </c>
       <c r="D228" s="3" t="n">
-        <v>8.159999847412109</v>
-      </c>
-      <c r="E228" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F228" s="8" t="inlineStr">
-        <is>
-          <t>A+</t>
+        <v>7.190000057220459</v>
+      </c>
+      <c r="E228" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F228" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -6921,16 +6921,16 @@
         <v>9</v>
       </c>
       <c r="D229" s="3" t="n">
-        <v>7.960000038146973</v>
-      </c>
-      <c r="E229" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F229" s="8" t="inlineStr">
-        <is>
-          <t>A+</t>
+        <v>7.150000095367432</v>
+      </c>
+      <c r="E229" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F229" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -6949,16 +6949,16 @@
         <v>9</v>
       </c>
       <c r="D230" s="3" t="n">
-        <v>8.029999732971191</v>
-      </c>
-      <c r="E230" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F230" s="8" t="inlineStr">
-        <is>
-          <t>A+</t>
+        <v>7.460000038146973</v>
+      </c>
+      <c r="E230" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F230" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -6977,14 +6977,14 @@
         <v>9</v>
       </c>
       <c r="D231" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="E231" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F231" s="8" t="inlineStr">
+        <v>7.599999904632568</v>
+      </c>
+      <c r="E231" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F231" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -7005,14 +7005,14 @@
         <v>10</v>
       </c>
       <c r="D232" s="3" t="n">
-        <v>8.979999542236328</v>
+        <v>8.609999656677246</v>
       </c>
       <c r="E232" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F232" s="7" t="inlineStr">
+      <c r="F232" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -7033,14 +7033,14 @@
         <v>10</v>
       </c>
       <c r="D233" s="3" t="n">
-        <v>9.020000457763672</v>
+        <v>8.560000419616699</v>
       </c>
       <c r="E233" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F233" s="7" t="inlineStr">
+      <c r="F233" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -7061,14 +7061,14 @@
         <v>10</v>
       </c>
       <c r="D234" s="3" t="n">
-        <v>9.119999885559082</v>
+        <v>8.789999961853027</v>
       </c>
       <c r="E234" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F234" s="7" t="inlineStr">
+      <c r="F234" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -7089,14 +7089,14 @@
         <v>10</v>
       </c>
       <c r="D235" s="3" t="n">
-        <v>9.279999732971191</v>
+        <v>8.75</v>
       </c>
       <c r="E235" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F235" s="7" t="inlineStr">
+      <c r="F235" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -7117,16 +7117,16 @@
         <v>10</v>
       </c>
       <c r="D236" s="3" t="n">
-        <v>9.5</v>
+        <v>8.960000038146973</v>
       </c>
       <c r="E236" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F236" s="9" t="inlineStr">
-        <is>
-          <t>AA</t>
+      <c r="F236" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
         </is>
       </c>
     </row>
@@ -7145,14 +7145,14 @@
         <v>10</v>
       </c>
       <c r="D237" s="3" t="n">
-        <v>9.479999542236328</v>
+        <v>9.210000038146973</v>
       </c>
       <c r="E237" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F237" s="7" t="inlineStr">
+      <c r="F237" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -7173,14 +7173,14 @@
         <v>10</v>
       </c>
       <c r="D238" s="3" t="n">
-        <v>9.479999542236328</v>
+        <v>9.149999618530273</v>
       </c>
       <c r="E238" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F238" s="7" t="inlineStr">
+      <c r="F238" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -7201,14 +7201,14 @@
         <v>10</v>
       </c>
       <c r="D239" s="3" t="n">
-        <v>9.449999809265137</v>
+        <v>9.039999961853027</v>
       </c>
       <c r="E239" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F239" s="7" t="inlineStr">
+      <c r="F239" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -7229,16 +7229,16 @@
         <v>10</v>
       </c>
       <c r="D240" s="3" t="n">
-        <v>9.630000114440918</v>
+        <v>8.890000343322754</v>
       </c>
       <c r="E240" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F240" s="9" t="inlineStr">
-        <is>
-          <t>AA</t>
+      <c r="F240" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
         </is>
       </c>
     </row>
@@ -7257,14 +7257,14 @@
         <v>10</v>
       </c>
       <c r="D241" s="3" t="n">
-        <v>9.489999771118164</v>
+        <v>8.850000381469727</v>
       </c>
       <c r="E241" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F241" s="7" t="inlineStr">
+      <c r="F241" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -7285,14 +7285,14 @@
         <v>10</v>
       </c>
       <c r="D242" s="3" t="n">
-        <v>9.470000267028809</v>
+        <v>8.590000152587891</v>
       </c>
       <c r="E242" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F242" s="7" t="inlineStr">
+      <c r="F242" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -7313,16 +7313,16 @@
         <v>9</v>
       </c>
       <c r="D243" s="3" t="n">
-        <v>8.319999694824219</v>
-      </c>
-      <c r="E243" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F243" s="8" t="inlineStr">
-        <is>
-          <t>A+</t>
+        <v>7.230000019073486</v>
+      </c>
+      <c r="E243" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F243" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -7341,14 +7341,14 @@
         <v>9</v>
       </c>
       <c r="D244" s="3" t="n">
-        <v>7.860000133514404</v>
-      </c>
-      <c r="E244" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F244" s="8" t="inlineStr">
+        <v>8.180000305175781</v>
+      </c>
+      <c r="E244" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F244" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -7369,16 +7369,16 @@
         <v>9</v>
       </c>
       <c r="D245" s="3" t="n">
-        <v>7.679999828338623</v>
-      </c>
-      <c r="E245" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F245" s="8" t="inlineStr">
-        <is>
-          <t>A+</t>
+        <v>7.440000057220459</v>
+      </c>
+      <c r="E245" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F245" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -7399,12 +7399,12 @@
       <c r="D246" s="3" t="n">
         <v>7.570000171661377</v>
       </c>
-      <c r="E246" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F246" s="8" t="inlineStr">
+      <c r="E246" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F246" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -7425,14 +7425,14 @@
         <v>9</v>
       </c>
       <c r="D247" s="3" t="n">
-        <v>7.510000228881836</v>
-      </c>
-      <c r="E247" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F247" s="8" t="inlineStr">
+        <v>7.730000019073486</v>
+      </c>
+      <c r="E247" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F247" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -7453,14 +7453,14 @@
         <v>9</v>
       </c>
       <c r="D248" s="3" t="n">
-        <v>7.539999961853027</v>
-      </c>
-      <c r="E248" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F248" s="8" t="inlineStr">
+        <v>7.889999866485596</v>
+      </c>
+      <c r="E248" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F248" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -7481,14 +7481,14 @@
         <v>9</v>
       </c>
       <c r="D249" s="3" t="n">
-        <v>7.650000095367432</v>
-      </c>
-      <c r="E249" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F249" s="8" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="E249" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F249" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -7509,14 +7509,14 @@
         <v>9</v>
       </c>
       <c r="D250" s="3" t="n">
-        <v>7.769999980926514</v>
-      </c>
-      <c r="E250" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F250" s="8" t="inlineStr">
+        <v>8.029999732971191</v>
+      </c>
+      <c r="E250" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F250" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -7537,14 +7537,14 @@
         <v>9</v>
       </c>
       <c r="D251" s="3" t="n">
-        <v>7.739999771118164</v>
-      </c>
-      <c r="E251" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F251" s="8" t="inlineStr">
+        <v>7.909999847412109</v>
+      </c>
+      <c r="E251" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F251" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -7565,14 +7565,14 @@
         <v>9</v>
       </c>
       <c r="D252" s="3" t="n">
-        <v>7.659999847412109</v>
-      </c>
-      <c r="E252" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F252" s="8" t="inlineStr">
+        <v>7.670000076293945</v>
+      </c>
+      <c r="E252" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F252" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -7593,14 +7593,14 @@
         <v>9</v>
       </c>
       <c r="D253" s="3" t="n">
-        <v>7.670000076293945</v>
-      </c>
-      <c r="E253" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F253" s="8" t="inlineStr">
+        <v>7.769999980926514</v>
+      </c>
+      <c r="E253" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F253" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -7621,14 +7621,14 @@
         <v>9</v>
       </c>
       <c r="D254" s="3" t="n">
-        <v>7.739999771118164</v>
-      </c>
-      <c r="E254" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F254" s="8" t="inlineStr">
+        <v>7.889999866485596</v>
+      </c>
+      <c r="E254" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F254" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -7649,14 +7649,14 @@
         <v>9</v>
       </c>
       <c r="D255" s="3" t="n">
-        <v>8.359999656677246</v>
-      </c>
-      <c r="E255" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F255" s="8" t="inlineStr">
+        <v>8.170000076293945</v>
+      </c>
+      <c r="E255" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F255" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -7677,14 +7677,14 @@
         <v>9</v>
       </c>
       <c r="D256" s="3" t="n">
-        <v>8.130000114440918</v>
-      </c>
-      <c r="E256" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F256" s="8" t="inlineStr">
+        <v>8.020000457763672</v>
+      </c>
+      <c r="E256" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F256" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -7705,14 +7705,14 @@
         <v>9</v>
       </c>
       <c r="D257" s="3" t="n">
-        <v>7.980000019073486</v>
-      </c>
-      <c r="E257" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F257" s="8" t="inlineStr">
+        <v>7.900000095367432</v>
+      </c>
+      <c r="E257" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F257" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -7733,16 +7733,16 @@
         <v>9</v>
       </c>
       <c r="D258" s="3" t="n">
-        <v>8.590000152587891</v>
-      </c>
-      <c r="E258" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F258" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+        <v>7.539999961853027</v>
+      </c>
+      <c r="E258" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F258" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -7761,16 +7761,16 @@
         <v>9</v>
       </c>
       <c r="D259" s="3" t="n">
-        <v>7.630000114440918</v>
-      </c>
-      <c r="E259" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F259" s="8" t="inlineStr">
-        <is>
-          <t>A+</t>
+        <v>7.190000057220459</v>
+      </c>
+      <c r="E259" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F259" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -7789,14 +7789,14 @@
         <v>9</v>
       </c>
       <c r="D260" s="3" t="n">
-        <v>7.849999904632568</v>
-      </c>
-      <c r="E260" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F260" s="8" t="inlineStr">
+        <v>7.579999923706055</v>
+      </c>
+      <c r="E260" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F260" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -7817,14 +7817,14 @@
         <v>9</v>
       </c>
       <c r="D261" s="3" t="n">
-        <v>7.889999866485596</v>
-      </c>
-      <c r="E261" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F261" s="8" t="inlineStr">
+        <v>7.639999866485596</v>
+      </c>
+      <c r="E261" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F261" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -7845,14 +7845,14 @@
         <v>9</v>
       </c>
       <c r="D262" s="3" t="n">
-        <v>7.880000114440918</v>
-      </c>
-      <c r="E262" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F262" s="8" t="inlineStr">
+        <v>7.699999809265137</v>
+      </c>
+      <c r="E262" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F262" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -7873,16 +7873,16 @@
         <v>9</v>
       </c>
       <c r="D263" s="3" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E263" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F263" s="8" t="inlineStr">
-        <is>
-          <t>A+</t>
+        <v>7.460000038146973</v>
+      </c>
+      <c r="E263" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F263" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -7901,9 +7901,9 @@
         <v>9</v>
       </c>
       <c r="D264" s="3" t="n">
-        <v>7.46999979019165</v>
-      </c>
-      <c r="E264" s="7" t="inlineStr">
+        <v>7.329999923706055</v>
+      </c>
+      <c r="E264" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -7929,16 +7929,16 @@
         <v>9</v>
       </c>
       <c r="D265" s="3" t="n">
-        <v>7.53000020980835</v>
-      </c>
-      <c r="E265" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="F265" s="8" t="inlineStr">
-        <is>
-          <t>A+</t>
+        <v>7.099999904632568</v>
+      </c>
+      <c r="E265" s="8" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="F265" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -7957,14 +7957,14 @@
         <v>10</v>
       </c>
       <c r="D266" s="3" t="n">
-        <v>7.579999923706055</v>
+        <v>8.149999618530273</v>
       </c>
       <c r="E266" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F266" s="8" t="inlineStr">
+      <c r="F266" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
@@ -7985,16 +7985,16 @@
         <v>10</v>
       </c>
       <c r="D267" s="3" t="n">
-        <v>8.520000457763672</v>
+        <v>7.199999809265137</v>
       </c>
       <c r="E267" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F267" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+      <c r="F267" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -8013,16 +8013,16 @@
         <v>10</v>
       </c>
       <c r="D268" s="3" t="n">
-        <v>8.670000076293945</v>
+        <v>7.809999942779541</v>
       </c>
       <c r="E268" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F268" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+      <c r="F268" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -8041,16 +8041,16 @@
         <v>10</v>
       </c>
       <c r="D269" s="3" t="n">
-        <v>8.600000381469727</v>
+        <v>7.710000038146973</v>
       </c>
       <c r="E269" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F269" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+      <c r="F269" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -8069,14 +8069,14 @@
         <v>10</v>
       </c>
       <c r="D270" s="3" t="n">
-        <v>8.789999961853027</v>
+        <v>8.520000457763672</v>
       </c>
       <c r="E270" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F270" s="7" t="inlineStr">
+      <c r="F270" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -8097,16 +8097,16 @@
         <v>10</v>
       </c>
       <c r="D271" s="3" t="n">
-        <v>8.779999732971191</v>
+        <v>8.119999885559082</v>
       </c>
       <c r="E271" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F271" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+      <c r="F271" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -8125,16 +8125,16 @@
         <v>10</v>
       </c>
       <c r="D272" s="3" t="n">
-        <v>8.659999847412109</v>
+        <v>7.840000152587891</v>
       </c>
       <c r="E272" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F272" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+      <c r="F272" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -8153,16 +8153,16 @@
         <v>10</v>
       </c>
       <c r="D273" s="3" t="n">
-        <v>8.909999847412109</v>
+        <v>8.329999923706055</v>
       </c>
       <c r="E273" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F273" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+      <c r="F273" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -8181,14 +8181,14 @@
         <v>10</v>
       </c>
       <c r="D274" s="3" t="n">
-        <v>8.979999542236328</v>
+        <v>8.819999694824219</v>
       </c>
       <c r="E274" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F274" s="7" t="inlineStr">
+      <c r="F274" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -8209,14 +8209,14 @@
         <v>10</v>
       </c>
       <c r="D275" s="3" t="n">
-        <v>8.909999847412109</v>
+        <v>8.850000381469727</v>
       </c>
       <c r="E275" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F275" s="7" t="inlineStr">
+      <c r="F275" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -8237,16 +8237,16 @@
         <v>10</v>
       </c>
       <c r="D276" s="3" t="n">
-        <v>8.670000076293945</v>
+        <v>7.380000114440918</v>
       </c>
       <c r="E276" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F276" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+      <c r="F276" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -8265,16 +8265,16 @@
         <v>10</v>
       </c>
       <c r="D277" s="3" t="n">
-        <v>9</v>
+        <v>8.470000267028809</v>
       </c>
       <c r="E277" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F277" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+      <c r="F277" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -8293,14 +8293,14 @@
         <v>10</v>
       </c>
       <c r="D278" s="3" t="n">
-        <v>8.970000267028809</v>
+        <v>8.789999961853027</v>
       </c>
       <c r="E278" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F278" s="7" t="inlineStr">
+      <c r="F278" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -8321,14 +8321,14 @@
         <v>10</v>
       </c>
       <c r="D279" s="3" t="n">
-        <v>8.989999771118164</v>
+        <v>8.789999961853027</v>
       </c>
       <c r="E279" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F279" s="7" t="inlineStr">
+      <c r="F279" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -8349,16 +8349,16 @@
         <v>10</v>
       </c>
       <c r="D280" s="3" t="n">
-        <v>8.909999847412109</v>
+        <v>8.359999656677246</v>
       </c>
       <c r="E280" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F280" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+      <c r="F280" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -8377,14 +8377,14 @@
         <v>10</v>
       </c>
       <c r="D281" s="3" t="n">
-        <v>9.050000190734863</v>
+        <v>8.819999694824219</v>
       </c>
       <c r="E281" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F281" s="7" t="inlineStr">
+      <c r="F281" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -8405,16 +8405,16 @@
         <v>10</v>
       </c>
       <c r="D282" s="3" t="n">
-        <v>8.960000038146973</v>
+        <v>8.100000381469727</v>
       </c>
       <c r="E282" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F282" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+      <c r="F282" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -8433,14 +8433,14 @@
         <v>10</v>
       </c>
       <c r="D283" s="3" t="n">
-        <v>8.909999847412109</v>
+        <v>8.710000038146973</v>
       </c>
       <c r="E283" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F283" s="7" t="inlineStr">
+      <c r="F283" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -8461,16 +8461,16 @@
         <v>10</v>
       </c>
       <c r="D284" s="3" t="n">
-        <v>8.819999694824219</v>
+        <v>8.300000190734863</v>
       </c>
       <c r="E284" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F284" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+      <c r="F284" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -8489,16 +8489,16 @@
         <v>10</v>
       </c>
       <c r="D285" s="3" t="n">
-        <v>8.489999771118164</v>
+        <v>6.289999961853027</v>
       </c>
       <c r="E285" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F285" s="8" t="inlineStr">
-        <is>
-          <t>A+</t>
+      <c r="F285" s="7" t="inlineStr">
+        <is>
+          <t>A-</t>
         </is>
       </c>
     </row>
@@ -8517,16 +8517,16 @@
         <v>10</v>
       </c>
       <c r="D286" s="3" t="n">
-        <v>8.909999847412109</v>
+        <v>6.599999904632568</v>
       </c>
       <c r="E286" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F286" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+      <c r="F286" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -8545,16 +8545,16 @@
         <v>10</v>
       </c>
       <c r="D287" s="3" t="n">
-        <v>9.289999961853027</v>
+        <v>7.380000114440918</v>
       </c>
       <c r="E287" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F287" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+      <c r="F287" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -8573,16 +8573,16 @@
         <v>10</v>
       </c>
       <c r="D288" s="3" t="n">
-        <v>8.640000343322754</v>
+        <v>7.670000076293945</v>
       </c>
       <c r="E288" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F288" s="7" t="inlineStr">
-        <is>
-          <t>AA-</t>
+      <c r="F288" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -8601,14 +8601,14 @@
         <v>10</v>
       </c>
       <c r="D289" s="3" t="n">
-        <v>9.270000457763672</v>
+        <v>8.619999885559082</v>
       </c>
       <c r="E289" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F289" s="7" t="inlineStr">
+      <c r="F289" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -8629,14 +8629,14 @@
         <v>10</v>
       </c>
       <c r="D290" s="3" t="n">
-        <v>9.279999732971191</v>
+        <v>8.819999694824219</v>
       </c>
       <c r="E290" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F290" s="7" t="inlineStr">
+      <c r="F290" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -8657,14 +8657,14 @@
         <v>10</v>
       </c>
       <c r="D291" s="3" t="n">
-        <v>9.220000267028809</v>
+        <v>8.960000038146973</v>
       </c>
       <c r="E291" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F291" s="7" t="inlineStr">
+      <c r="F291" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -8685,14 +8685,14 @@
         <v>10</v>
       </c>
       <c r="D292" s="3" t="n">
-        <v>9.229999542236328</v>
+        <v>9.060000419616699</v>
       </c>
       <c r="E292" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F292" s="7" t="inlineStr">
+      <c r="F292" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -8713,14 +8713,14 @@
         <v>10</v>
       </c>
       <c r="D293" s="3" t="n">
-        <v>9.289999961853027</v>
+        <v>9.109999656677246</v>
       </c>
       <c r="E293" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F293" s="7" t="inlineStr">
+      <c r="F293" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -8741,14 +8741,14 @@
         <v>10</v>
       </c>
       <c r="D294" s="3" t="n">
-        <v>9.399999618530273</v>
+        <v>8.979999542236328</v>
       </c>
       <c r="E294" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F294" s="7" t="inlineStr">
+      <c r="F294" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -8769,14 +8769,14 @@
         <v>10</v>
       </c>
       <c r="D295" s="3" t="n">
-        <v>9.390000343322754</v>
+        <v>9.170000076293945</v>
       </c>
       <c r="E295" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F295" s="7" t="inlineStr">
+      <c r="F295" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -8797,14 +8797,14 @@
         <v>10</v>
       </c>
       <c r="D296" s="3" t="n">
-        <v>9.100000381469727</v>
+        <v>8.829999923706055</v>
       </c>
       <c r="E296" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F296" s="7" t="inlineStr">
+      <c r="F296" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -8825,14 +8825,14 @@
         <v>10</v>
       </c>
       <c r="D297" s="3" t="n">
-        <v>8.909999847412109</v>
+        <v>8.630000114440918</v>
       </c>
       <c r="E297" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F297" s="7" t="inlineStr">
+      <c r="F297" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -8853,14 +8853,14 @@
         <v>10</v>
       </c>
       <c r="D298" s="3" t="n">
-        <v>9.060000419616699</v>
+        <v>8.989999771118164</v>
       </c>
       <c r="E298" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F298" s="7" t="inlineStr">
+      <c r="F298" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -8881,14 +8881,14 @@
         <v>10</v>
       </c>
       <c r="D299" s="3" t="n">
-        <v>8.979999542236328</v>
+        <v>9.319999694824219</v>
       </c>
       <c r="E299" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F299" s="7" t="inlineStr">
+      <c r="F299" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -8909,14 +8909,14 @@
         <v>10</v>
       </c>
       <c r="D300" s="3" t="n">
-        <v>9.239999771118164</v>
+        <v>9.210000038146973</v>
       </c>
       <c r="E300" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F300" s="7" t="inlineStr">
+      <c r="F300" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -8937,14 +8937,14 @@
         <v>10</v>
       </c>
       <c r="D301" s="3" t="n">
-        <v>9.130000114440918</v>
+        <v>9.229999542236328</v>
       </c>
       <c r="E301" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F301" s="7" t="inlineStr">
+      <c r="F301" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -8965,14 +8965,14 @@
         <v>10</v>
       </c>
       <c r="D302" s="3" t="n">
-        <v>9.029999732971191</v>
+        <v>9.270000457763672</v>
       </c>
       <c r="E302" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F302" s="7" t="inlineStr">
+      <c r="F302" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -8993,14 +8993,14 @@
         <v>10</v>
       </c>
       <c r="D303" s="3" t="n">
-        <v>8.890000343322754</v>
+        <v>8.710000038146973</v>
       </c>
       <c r="E303" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F303" s="7" t="inlineStr">
+      <c r="F303" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -9021,14 +9021,14 @@
         <v>10</v>
       </c>
       <c r="D304" s="3" t="n">
-        <v>8.880000114440918</v>
+        <v>8.75</v>
       </c>
       <c r="E304" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F304" s="7" t="inlineStr">
+      <c r="F304" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -9049,14 +9049,14 @@
         <v>10</v>
       </c>
       <c r="D305" s="3" t="n">
-        <v>8.930000305175781</v>
+        <v>8.939999580383301</v>
       </c>
       <c r="E305" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F305" s="7" t="inlineStr">
+      <c r="F305" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -9077,14 +9077,14 @@
         <v>10</v>
       </c>
       <c r="D306" s="3" t="n">
-        <v>8.899999618530273</v>
+        <v>9.199999809265137</v>
       </c>
       <c r="E306" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F306" s="7" t="inlineStr">
+      <c r="F306" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -9105,14 +9105,14 @@
         <v>10</v>
       </c>
       <c r="D307" s="3" t="n">
-        <v>8.510000228881836</v>
+        <v>8.989999771118164</v>
       </c>
       <c r="E307" s="9" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F307" s="7" t="inlineStr">
+      <c r="F307" s="8" t="inlineStr">
         <is>
           <t>AA-</t>
         </is>
@@ -9133,16 +9133,16 @@
         <v>8</v>
       </c>
       <c r="D308" s="3" t="n">
-        <v>7.099999904632568</v>
-      </c>
-      <c r="E308" s="8" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="F308" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
+        <v>6.489999771118164</v>
+      </c>
+      <c r="E308" s="5" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="F308" s="7" t="inlineStr">
+        <is>
+          <t>A-</t>
         </is>
       </c>
     </row>
@@ -9161,9 +9161,9 @@
         <v>8</v>
       </c>
       <c r="D309" s="3" t="n">
-        <v>7.210000038146973</v>
-      </c>
-      <c r="E309" s="8" t="inlineStr">
+        <v>6.599999904632568</v>
+      </c>
+      <c r="E309" s="5" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
